--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 600 AHO QC COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 600 AHO QC COPART SR.xlsx
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Bocaiuva do Sul</t>
+          <t>Bocaiúva do Sul</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
@@ -21452,7 +21452,7 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
@@ -21754,7 +21754,7 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
@@ -31224,7 +31224,7 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
@@ -31278,7 +31278,7 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
@@ -31440,7 +31440,7 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G541" s="2" t="inlineStr">
@@ -31548,7 +31548,7 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G542" s="2" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G543" s="2" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G544" s="2" t="inlineStr">
@@ -31710,7 +31710,7 @@
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G545" s="2" t="inlineStr">
@@ -31764,7 +31764,7 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G546" s="2" t="inlineStr">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G547" s="2" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G548" s="2" t="inlineStr">
@@ -31926,7 +31926,7 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G549" s="2" t="inlineStr">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G550" s="2" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G551" s="2" t="inlineStr">
@@ -32088,7 +32088,7 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G553" s="2" t="inlineStr">
@@ -32200,7 +32200,7 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G555" s="2" t="inlineStr">
@@ -32312,7 +32312,7 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
@@ -32420,7 +32420,7 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G559" s="2" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
@@ -32766,7 +32766,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32776,7 +32776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32886,7 +32886,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bocaiuva do Sul</t>
+          <t>Bocaiúva do Sul</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -32896,7 +32896,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="B34" t="n">

--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 600 AHO QC COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 600 AHO QC COPART SR.xlsx
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6B4E"/>
+        <fgColor rgb="008E0E28"/>
       </patternFill>
     </fill>
   </fills>
